--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_6_ablation_and_lag_resolution_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_6_ablation_and_lag_resolution_source_data.xlsx
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1137566137566137</v>
+        <v>-0.1060405643738977</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1519636558327034</v>
+        <v>-0.1355702003023433</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08061775636180397</v>
+        <v>-0.08106261022927701</v>
       </c>
       <c r="G2" t="n">
         <v>126</v>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05076845553036036</v>
+        <v>-0.04617031997984389</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.07094041320231795</v>
+        <v>-0.072122228521038</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.03199011085915836</v>
+        <v>-0.02052941546989169</v>
       </c>
       <c r="G3" t="n">
         <v>126</v>
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03609221466364321</v>
+        <v>0.05165028974552788</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02097505668934252</v>
+        <v>0.03472930839002263</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05138259007306624</v>
+        <v>0.06991843033509691</v>
       </c>
       <c r="G4" t="n">
         <v>126</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.002047115142353229</v>
+        <v>-0.009101788863693616</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01178114764424285</v>
+        <v>-0.02358985260770984</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008727796674225246</v>
+        <v>0.003750157470395496</v>
       </c>
       <c r="G5" t="n">
         <v>126</v>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.298815822625148e-05</v>
+        <v>-0.0007243638196018365</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0002834467120181872</v>
+        <v>-0.001574703955656287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0004409171075838714</v>
+        <v>6.298815822614046e-05</v>
       </c>
       <c r="G6" t="n">
         <v>126</v>
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.03426555807508169</v>
+        <v>-0.01817208364827416</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05442649281934991</v>
+        <v>-0.03792044595616027</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0143502771478962</v>
+        <v>0.00245338876291253</v>
       </c>
       <c r="G7" t="n">
         <v>126</v>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.03155706727135288</v>
+        <v>-0.04075333837238604</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04724584278155702</v>
+        <v>-0.06450853489543963</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01662729906777518</v>
+        <v>-0.01482741244646</v>
       </c>
       <c r="G8" t="n">
         <v>126</v>
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.005353993449231487</v>
+        <v>-0.003779289493575311</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01792170571932481</v>
+        <v>-0.02630542957923911</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006936570924666159</v>
+        <v>0.01531872008062479</v>
       </c>
       <c r="G9" t="n">
         <v>126</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.006267321743512189</v>
+        <v>-0.01565255731922399</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01848781179138325</v>
+        <v>-0.0305209120685311</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004697341899722758</v>
+        <v>-0.001195987654320955</v>
       </c>
       <c r="G10" t="n">
         <v>126</v>
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>9.448223733932171e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0003779289493574006</v>
+        <v>-0.00066216301335352</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0003464348702443304</v>
+        <v>0.001040091962710925</v>
       </c>
       <c r="G11" t="n">
         <v>126</v>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1276455026455026</v>
+        <v>-0.1170634920634923</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1508432539682539</v>
+        <v>-0.1431807445200302</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1006212207105063</v>
+        <v>-0.09073286722096253</v>
       </c>
       <c r="G12" t="n">
         <v>126</v>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02976190476190477</v>
+        <v>0.03546233308138058</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01350151171579751</v>
+        <v>0.01523604812295296</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0431791698160746</v>
+        <v>0.05578310027714786</v>
       </c>
       <c r="G13" t="n">
         <v>126</v>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01773116654069029</v>
+        <v>-0.009448223733938055</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04375551146384481</v>
+        <v>-0.03560169438145638</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006303539934492337</v>
+        <v>0.01959719072814315</v>
       </c>
       <c r="G14" t="n">
         <v>126</v>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01234567901234573</v>
+        <v>0.004913076341647726</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0004637503149407229</v>
+        <v>-0.008989984882841914</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02585978835978837</v>
+        <v>0.02015857268833451</v>
       </c>
       <c r="G15" t="n">
         <v>126</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.0001574703955656842</v>
+        <v>0.0003149407911312574</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0003787163013353356</v>
+        <v>-0.0002527399848829409</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000818846056941272</v>
+        <v>0.001040091962711139</v>
       </c>
       <c r="G16" t="n">
         <v>126</v>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07420005039052663</v>
+        <v>-0.07561728395061723</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09275636180398103</v>
+        <v>-0.0963411753590324</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06021431720836481</v>
+        <v>-0.05989465230536654</v>
       </c>
       <c r="G17" t="n">
         <v>126</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02188838498362311</v>
+        <v>0.01455026455026465</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01058201058201069</v>
+        <v>0.006297241118669608</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03521589191232048</v>
+        <v>0.02497480473670944</v>
       </c>
       <c r="G18" t="n">
         <v>126</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03454900478709999</v>
+        <v>0.03228143109095494</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0220112118921643</v>
+        <v>0.01930272108843548</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04919532627865961</v>
+        <v>0.04693562610229284</v>
       </c>
       <c r="G19" t="n">
         <v>126</v>
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01565255731922388</v>
+        <v>0.008849836230788721</v>
       </c>
       <c r="E20" t="n">
-        <v>0.004940633660871766</v>
+        <v>-0.001170792391030609</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02932098765432101</v>
+        <v>0.02097820609725383</v>
       </c>
       <c r="G20" t="n">
         <v>126</v>
@@ -1034,13 +1034,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.0007243638196017255</v>
+        <v>0.0003464348702444386</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.377551020418366e-05</v>
+        <v>-0.0004409171075837603</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00167076089695148</v>
+        <v>0.001292044595616037</v>
       </c>
       <c r="G21" t="n">
         <v>126</v>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.04517374517374517</v>
+        <v>0.0553352559480894</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.01271271622253389</v>
+        <v>-0.007518811334975407</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1140234866504891</v>
+        <v>0.1200043859649123</v>
       </c>
       <c r="G22" t="n">
         <v>126</v>
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.05945945945945946</v>
+        <v>0.08406432748538012</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01608026147314509</v>
+        <v>0.02737865805187362</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1185580065359476</v>
+        <v>0.1466077898550724</v>
       </c>
       <c r="G23" t="n">
         <v>126</v>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.002565856996236744</v>
+        <v>-0.0131578947368421</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.04128019769238658</v>
+        <v>-0.04288865546218487</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03413301295654237</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>126</v>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.01644415499837187</v>
+        <v>-0.0131578947368421</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0626015076653451</v>
+        <v>-0.04001351351351352</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02381651243493348</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>126</v>

--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_6_ablation_and_lag_resolution_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_6_ablation_and_lag_resolution_source_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,7 +462,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>n_clusters</t>
+          <t>n_window_clusters</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_process_time_blocks</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bootstrap_unit</t>
         </is>
       </c>
     </row>
@@ -486,13 +496,21 @@
         <v>-0.1060405643738977</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1355702003023433</v>
+        <v>-0.1238201910666887</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08106261022927701</v>
+        <v>-0.08857173906574164</v>
       </c>
       <c r="G2" t="n">
         <v>126</v>
+      </c>
+      <c r="H2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -515,13 +533,21 @@
         <v>-0.04617031997984389</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.072122228521038</v>
+        <v>-0.06969029681318213</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02052941546989169</v>
+        <v>-0.02304807692307687</v>
       </c>
       <c r="G3" t="n">
         <v>126</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -544,13 +570,21 @@
         <v>0.05165028974552788</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03472930839002263</v>
+        <v>0.03164712126494166</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06991843033509691</v>
+        <v>0.07131937064188189</v>
       </c>
       <c r="G4" t="n">
         <v>126</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -573,13 +607,21 @@
         <v>-0.009101788863693616</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02358985260770984</v>
+        <v>-0.0270030699688933</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003750157470395496</v>
+        <v>0.01177854906242313</v>
       </c>
       <c r="G5" t="n">
         <v>126</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -602,13 +644,21 @@
         <v>-0.0007243638196018365</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001574703955656287</v>
+        <v>-0.001344544120707608</v>
       </c>
       <c r="F6" t="n">
-        <v>6.298815822614046e-05</v>
+        <v>3.117024003419218e-05</v>
       </c>
       <c r="G6" t="n">
         <v>126</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -631,13 +681,21 @@
         <v>-0.01817208364827416</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03792044595616027</v>
+        <v>-0.0369359851933749</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00245338876291253</v>
+        <v>-0.002217297925638767</v>
       </c>
       <c r="G7" t="n">
         <v>126</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -660,13 +718,21 @@
         <v>-0.04075333837238604</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06450853489543963</v>
+        <v>-0.0667327772733456</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.01482741244646</v>
+        <v>-0.01579835390218514</v>
       </c>
       <c r="G8" t="n">
         <v>126</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -689,13 +755,21 @@
         <v>-0.003779289493575311</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02630542957923911</v>
+        <v>-0.02805312953368128</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01531872008062479</v>
+        <v>0.01664418819444458</v>
       </c>
       <c r="G9" t="n">
         <v>126</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -718,13 +792,21 @@
         <v>-0.01565255731922399</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0305209120685311</v>
+        <v>-0.03104086387804045</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.001195987654320955</v>
+        <v>0.001821854958677564</v>
       </c>
       <c r="G10" t="n">
         <v>126</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -747,13 +829,21 @@
         <v>9.448223733932171e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.00066216301335352</v>
+        <v>-0.0006580388735398568</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001040091962710925</v>
+        <v>0.0007215589635020582</v>
       </c>
       <c r="G11" t="n">
         <v>126</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -776,13 +866,21 @@
         <v>-0.1170634920634923</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1431807445200302</v>
+        <v>-0.140217801674427</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09073286722096253</v>
+        <v>-0.09283666203252805</v>
       </c>
       <c r="G12" t="n">
         <v>126</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -805,13 +903,21 @@
         <v>0.03546233308138058</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01523604812295296</v>
+        <v>0.01634594245836643</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05578310027714786</v>
+        <v>0.05561350033608699</v>
       </c>
       <c r="G13" t="n">
         <v>126</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -834,13 +940,21 @@
         <v>-0.009448223733938055</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03560169438145638</v>
+        <v>-0.04412434218142063</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01959719072814315</v>
+        <v>0.01524562715470714</v>
       </c>
       <c r="G14" t="n">
         <v>126</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -863,13 +977,21 @@
         <v>0.004913076341647726</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008989984882841914</v>
+        <v>-0.008168095405156528</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02015857268833451</v>
+        <v>0.02114507030601484</v>
       </c>
       <c r="G15" t="n">
         <v>126</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -892,13 +1014,21 @@
         <v>0.0003149407911312574</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0002527399848829409</v>
+        <v>-0.0002473386291129864</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001040091962711139</v>
+        <v>0.001216335605491531</v>
       </c>
       <c r="G16" t="n">
         <v>126</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -921,13 +1051,21 @@
         <v>-0.07561728395061723</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0963411753590324</v>
+        <v>-0.09652157658680781</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05989465230536654</v>
+        <v>-0.06033323917802415</v>
       </c>
       <c r="G17" t="n">
         <v>126</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -950,13 +1088,21 @@
         <v>0.01455026455026465</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006297241118669608</v>
+        <v>0.006817812547083771</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02497480473670944</v>
+        <v>0.0201492007102864</v>
       </c>
       <c r="G18" t="n">
         <v>126</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -979,13 +1125,21 @@
         <v>0.03228143109095494</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01930272108843548</v>
+        <v>0.02011404804309412</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04693562610229284</v>
+        <v>0.04522790701865565</v>
       </c>
       <c r="G19" t="n">
         <v>126</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1008,13 +1162,21 @@
         <v>0.008849836230788721</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.001170792391030609</v>
+        <v>0.001697312012692806</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02097820609725383</v>
+        <v>0.0186512170881806</v>
       </c>
       <c r="G20" t="n">
         <v>126</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1037,13 +1199,21 @@
         <v>0.0003464348702444386</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0004409171075837603</v>
+        <v>-0.0004101553436716587</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001292044595616037</v>
+        <v>0.00114773243771407</v>
       </c>
       <c r="G21" t="n">
         <v>126</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1066,13 +1236,21 @@
         <v>0.0553352559480894</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.007518811334975407</v>
+        <v>-0.000784126541083688</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1200043859649123</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="G22" t="n">
         <v>126</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1095,13 +1273,21 @@
         <v>0.08406432748538012</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02737865805187362</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1466077898550724</v>
+        <v>0.1587474120082815</v>
       </c>
       <c r="G23" t="n">
         <v>126</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1124,7 +1310,7 @@
         <v>-0.0131578947368421</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.04288865546218487</v>
+        <v>-0.03798685491723466</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1132,6 +1318,14 @@
       <c r="G24" t="n">
         <v>126</v>
       </c>
+      <c r="H24" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1153,7 +1347,7 @@
         <v>-0.0131578947368421</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.04001351351351352</v>
+        <v>-0.03658536585365853</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1161,6 +1355,14 @@
       <c r="G25" t="n">
         <v>126</v>
       </c>
+      <c r="H25" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1391,14 @@
       </c>
       <c r="G26" t="n">
         <v>126</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>synchronized_7d_process_time_block_all_pairs</t>
+        </is>
       </c>
     </row>
   </sheetData>
